--- a/3_Code/output/perhitungan_persentase_before_after_kmeans.xlsx
+++ b/3_Code/output/perhitungan_persentase_before_after_kmeans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IPB\TESIS\PENELITIAN\CODE\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F2045C-5EAD-4233-83F7-D20987025BB9}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89FBD7DE-6D0E-4AEB-BE90-85F4F6BAE415}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{775CFF51-0C88-4827-8E2F-4B29B2EF125C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
   <si>
     <t>Jarak</t>
   </si>
@@ -46,13 +46,46 @@
   </si>
   <si>
     <t>Rata-rata</t>
+  </si>
+  <si>
+    <t>Jarak tempuh (Km)</t>
+  </si>
+  <si>
+    <t>Standar deviasi jumlah paket diterima kurir</t>
+  </si>
+  <si>
+    <t>K-MEANS</t>
+  </si>
+  <si>
+    <t>VORONOI</t>
+  </si>
+  <si>
+    <t>algoritma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penerapan </t>
+  </si>
+  <si>
+    <t>Selisih standar deviasi (%)</t>
+  </si>
+  <si>
+    <t>Selisih jarak tempuh (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sesudah </t>
+  </si>
+  <si>
+    <t>Sebelum penerapan algoritma</t>
+  </si>
+  <si>
+    <t>Tanggal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -73,6 +106,21 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -82,7 +130,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -151,12 +199,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -185,6 +262,48 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -501,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C471EE7D-889F-4DC3-AD5B-0FE70F47C8AE}">
-  <dimension ref="B1:H8"/>
+  <dimension ref="B1:H30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -517,6 +636,9 @@
       </c>
     </row>
     <row r="2" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
       <c r="C2" t="s">
         <v>0</v>
       </c>
@@ -674,7 +796,363 @@
         <v>0.29969948200513452</v>
       </c>
     </row>
+    <row r="10" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="2:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="1">
+        <v>45866</v>
+      </c>
+      <c r="C12" s="12">
+        <v>1178.3800000000001</v>
+      </c>
+      <c r="D12" s="13">
+        <v>32.409999999999997</v>
+      </c>
+      <c r="E12" s="12">
+        <v>1177.06</v>
+      </c>
+      <c r="F12" s="13">
+        <v>32.42</v>
+      </c>
+      <c r="G12" s="8">
+        <f>(E12-C12)/C12</f>
+        <v>-1.1201819447038846E-3</v>
+      </c>
+      <c r="H12" s="9">
+        <f>(F12-D12)/D12</f>
+        <v>3.0854674483199988E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="4">
+        <v>45867</v>
+      </c>
+      <c r="C13" s="12">
+        <v>1036.4000000000001</v>
+      </c>
+      <c r="D13" s="13">
+        <v>25.19</v>
+      </c>
+      <c r="E13" s="12">
+        <v>1035.25</v>
+      </c>
+      <c r="F13" s="13">
+        <v>25.19</v>
+      </c>
+      <c r="G13" s="8">
+        <f t="shared" ref="G13:G16" si="2">(E13-C13)/C13</f>
+        <v>-1.1096101891162589E-3</v>
+      </c>
+      <c r="H13" s="9">
+        <f t="shared" ref="H13:H16" si="3">(F13-D13)/D13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="4">
+        <v>45875</v>
+      </c>
+      <c r="C14" s="12">
+        <v>1001.26</v>
+      </c>
+      <c r="D14" s="13">
+        <v>26.29</v>
+      </c>
+      <c r="E14" s="12">
+        <v>1000.14</v>
+      </c>
+      <c r="F14" s="13">
+        <v>26.29</v>
+      </c>
+      <c r="G14" s="8">
+        <f t="shared" si="2"/>
+        <v>-1.1185905758744029E-3</v>
+      </c>
+      <c r="H14" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="4">
+        <v>45876</v>
+      </c>
+      <c r="C15" s="12">
+        <v>1268.1500000000001</v>
+      </c>
+      <c r="D15" s="13">
+        <v>34.479999999999997</v>
+      </c>
+      <c r="E15" s="12">
+        <v>1266.73</v>
+      </c>
+      <c r="F15" s="13">
+        <v>34.479999999999997</v>
+      </c>
+      <c r="G15" s="8">
+        <f t="shared" si="2"/>
+        <v>-1.1197413555179376E-3</v>
+      </c>
+      <c r="H15" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="4">
+        <v>45889</v>
+      </c>
+      <c r="C16" s="14">
+        <v>1063.0999999999999</v>
+      </c>
+      <c r="D16" s="15">
+        <v>22.49</v>
+      </c>
+      <c r="E16" s="15">
+        <v>1061.9100000000001</v>
+      </c>
+      <c r="F16" s="15">
+        <v>22.49</v>
+      </c>
+      <c r="G16" s="8">
+        <f t="shared" si="2"/>
+        <v>-1.1193678863698874E-3</v>
+      </c>
+      <c r="H16" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G17" s="10">
+        <f>AVERAGE(G12:G16)</f>
+        <v>-1.1174983903164744E-3</v>
+      </c>
+      <c r="H17" s="10">
+        <f>AVERAGE(H12:H16)</f>
+        <v>6.1709348966399981E-5</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="23"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+    </row>
+    <row r="23" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="22"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="19"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+    </row>
+    <row r="24" spans="2:8" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="19"/>
+      <c r="C24" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+    </row>
+    <row r="25" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="18">
+        <v>45866</v>
+      </c>
+      <c r="C25" s="12">
+        <v>1865.53</v>
+      </c>
+      <c r="D25" s="13">
+        <v>27.32</v>
+      </c>
+      <c r="E25" s="12">
+        <v>1797.77</v>
+      </c>
+      <c r="F25" s="13">
+        <v>0.16</v>
+      </c>
+      <c r="G25" s="8">
+        <f>(E25-C25)/C25</f>
+        <v>-3.6322117575166304E-2</v>
+      </c>
+      <c r="H25" s="9">
+        <f>(F25-D25)/D25</f>
+        <v>-0.99414348462664714</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="18">
+        <v>45867</v>
+      </c>
+      <c r="C26" s="12">
+        <v>1656.21</v>
+      </c>
+      <c r="D26" s="13">
+        <v>20.53</v>
+      </c>
+      <c r="E26" s="12">
+        <v>1372.74</v>
+      </c>
+      <c r="F26" s="13">
+        <v>1.96</v>
+      </c>
+      <c r="G26" s="8">
+        <f t="shared" ref="G26:G29" si="4">(E26-C26)/C26</f>
+        <v>-0.1711558316880106</v>
+      </c>
+      <c r="H26" s="9">
+        <f t="shared" ref="H26:H29" si="5">(F26-D26)/D26</f>
+        <v>-0.9045299561617145</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="18">
+        <v>45875</v>
+      </c>
+      <c r="C27" s="12">
+        <v>1540.26</v>
+      </c>
+      <c r="D27" s="13">
+        <v>18.91</v>
+      </c>
+      <c r="E27" s="12">
+        <v>1399.02</v>
+      </c>
+      <c r="F27" s="13">
+        <v>0.51</v>
+      </c>
+      <c r="G27" s="8">
+        <f t="shared" si="4"/>
+        <v>-9.1698804098009429E-2</v>
+      </c>
+      <c r="H27" s="9">
+        <f t="shared" si="5"/>
+        <v>-0.97303014278159694</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="18">
+        <v>45876</v>
+      </c>
+      <c r="C28" s="17">
+        <v>2121</v>
+      </c>
+      <c r="D28" s="13">
+        <v>24.88</v>
+      </c>
+      <c r="E28" s="12">
+        <v>1834.42</v>
+      </c>
+      <c r="F28" s="13">
+        <v>0.46</v>
+      </c>
+      <c r="G28" s="8">
+        <f t="shared" si="4"/>
+        <v>-0.13511551155115509</v>
+      </c>
+      <c r="H28" s="9">
+        <f t="shared" si="5"/>
+        <v>-0.98151125401929262</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="16">
+        <v>45889</v>
+      </c>
+      <c r="C29" s="14">
+        <v>1721.48</v>
+      </c>
+      <c r="D29" s="15">
+        <v>17.18</v>
+      </c>
+      <c r="E29" s="14">
+        <v>1331.44</v>
+      </c>
+      <c r="F29" s="15">
+        <v>1.29</v>
+      </c>
+      <c r="G29" s="8">
+        <f t="shared" si="4"/>
+        <v>-0.22657248414155259</v>
+      </c>
+      <c r="H29" s="9">
+        <f t="shared" si="5"/>
+        <v>-0.92491268917345759</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G30" s="10">
+        <f>AVERAGE(G25:G29)</f>
+        <v>-0.13217294981077882</v>
+      </c>
+      <c r="H30" s="10">
+        <f>AVERAGE(H25:H29)</f>
+        <v>-0.95562550535254176</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="H21:H24"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="C21:D23"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G21:G24"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/3_Code/output/perhitungan_persentase_before_after_kmeans.xlsx
+++ b/3_Code/output/perhitungan_persentase_before_after_kmeans.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IPB\TESIS\PENELITIAN\CODE\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\tesis\3_Code\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89FBD7DE-6D0E-4AEB-BE90-85F4F6BAE415}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C0BD3B-ED91-4445-98DD-1464A45E8A36}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{775CFF51-0C88-4827-8E2F-4B29B2EF125C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
   <si>
     <t>Jarak</t>
   </si>
@@ -79,13 +79,43 @@
   </si>
   <si>
     <t>Tanggal</t>
+  </si>
+  <si>
+    <r>
+      <t>Jain fairness index</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> jumlah paket</t>
+    </r>
+  </si>
+  <si>
+    <t>Selisih (%)</t>
+  </si>
+  <si>
+    <t>K-Means</t>
+  </si>
+  <si>
+    <t>Capacity Constraint Voronoi Diagram</t>
+  </si>
+  <si>
+    <t>Ant Colony Optimization</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="170" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,6 +151,27 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="DengXian"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -233,7 +284,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -290,19 +341,46 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -620,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C471EE7D-889F-4DC3-AD5B-0FE70F47C8AE}">
-  <dimension ref="B1:H30"/>
+  <dimension ref="B1:H42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -951,21 +1029,21 @@
     </row>
     <row r="20" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24" t="s">
+      <c r="D21" s="21"/>
+      <c r="E21" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24" t="s">
+      <c r="F21" s="21"/>
+      <c r="G21" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="H21" s="24" t="s">
+      <c r="H21" s="21" t="s">
         <v>13</v>
       </c>
     </row>
@@ -973,40 +1051,40 @@
       <c r="B22" s="22"/>
       <c r="C22" s="22"/>
       <c r="D22" s="22"/>
-      <c r="E22" s="23" t="s">
+      <c r="E22" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="23"/>
+      <c r="F22" s="24"/>
       <c r="G22" s="22"/>
       <c r="H22" s="22"/>
     </row>
     <row r="23" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="22"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19" t="s">
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F23" s="19"/>
+      <c r="F23" s="23"/>
       <c r="G23" s="22"/>
       <c r="H23" s="22"/>
     </row>
     <row r="24" spans="2:8" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="19"/>
-      <c r="C24" s="20" t="s">
+      <c r="B24" s="23"/>
+      <c r="C24" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="21" t="s">
+      <c r="D24" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="F24" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
     </row>
     <row r="25" spans="2:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="18">
@@ -1143,8 +1221,157 @@
         <v>-0.95562550535254176</v>
       </c>
     </row>
+    <row r="34" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="2:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="23"/>
+      <c r="C36" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F36" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="23"/>
+    </row>
+    <row r="37" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B37" s="26">
+        <v>45866</v>
+      </c>
+      <c r="C37" s="27">
+        <v>0.93500000000000005</v>
+      </c>
+      <c r="D37" s="33">
+        <v>0.91</v>
+      </c>
+      <c r="E37" s="27">
+        <v>1</v>
+      </c>
+      <c r="F37" s="27">
+        <v>1</v>
+      </c>
+      <c r="G37" s="32">
+        <f>F37-C37/C37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B38" s="26">
+        <v>45867</v>
+      </c>
+      <c r="C38" s="27">
+        <v>0.94099999999999995</v>
+      </c>
+      <c r="D38" s="27">
+        <v>0.91400000000000003</v>
+      </c>
+      <c r="E38" s="27">
+        <v>0.999</v>
+      </c>
+      <c r="F38" s="27">
+        <v>0.999</v>
+      </c>
+      <c r="G38" s="32">
+        <f t="shared" ref="G38:G41" si="6">F38-C38/C38</f>
+        <v>-1.0000000000000009E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B39" s="26">
+        <v>45875</v>
+      </c>
+      <c r="C39" s="27">
+        <v>0.94599999999999995</v>
+      </c>
+      <c r="D39" s="27">
+        <v>0.90100000000000002</v>
+      </c>
+      <c r="E39" s="27">
+        <v>1</v>
+      </c>
+      <c r="F39" s="27">
+        <v>1</v>
+      </c>
+      <c r="G39" s="32">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B40" s="26">
+        <v>45876</v>
+      </c>
+      <c r="C40" s="27">
+        <v>0.94299999999999995</v>
+      </c>
+      <c r="D40" s="27">
+        <v>0.89600000000000002</v>
+      </c>
+      <c r="E40" s="27">
+        <v>1</v>
+      </c>
+      <c r="F40" s="27">
+        <v>1</v>
+      </c>
+      <c r="G40" s="32">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="28">
+        <v>45889</v>
+      </c>
+      <c r="C41" s="29">
+        <v>0.96099999999999997</v>
+      </c>
+      <c r="D41" s="29">
+        <v>0.93500000000000005</v>
+      </c>
+      <c r="E41" s="29">
+        <v>1</v>
+      </c>
+      <c r="F41" s="29">
+        <v>1</v>
+      </c>
+      <c r="G41" s="32">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="30"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="10">
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="G35:G36"/>
     <mergeCell ref="H21:H24"/>
     <mergeCell ref="B21:B24"/>
     <mergeCell ref="C21:D23"/>
